--- a/public/crawlability-laguna-water-september-2026.xlsx
+++ b/public/crawlability-laguna-water-september-2026.xlsx
@@ -585,7 +585,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של laguna-water ב-SE Ranking (הסריקה האחרונה: 2026-02-02).</t>
+          <t>להריץ מחדש את ה-Website Audit של laguna-water ב-SE Ranking (הסריקה האחרונה: 2026-02-02); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
         </is>
       </c>
     </row>

--- a/public/crawlability-laguna-water-september-2026.xlsx
+++ b/public/crawlability-laguna-water-september-2026.xlsx
@@ -563,9 +563,9 @@
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>קישורי Cloudflare (ללא טיפול)</t>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">

--- a/public/crawlability-laguna-water-september-2026.xlsx
+++ b/public/crawlability-laguna-water-september-2026.xlsx
@@ -741,7 +741,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>הפניה זמנית (302) לעמוד קיים. להמיר להפניית 301 ליעד ולעדכן את הקישורים הפנימיים ישירות ליעד.</t>
+          <t>הפניה זמנית (302) לעמוד קיים. אם ההפניה מכוונת וקבועה, להמיר להפניית 301 ליעד ולעדכן את הקישורים הפנימיים ישירות ליעד; אם הכתובת המקורית אמורה לחזור, לבטל את ההפניה.</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr">

--- a/public/crawlability-laguna-water-september-2026.xlsx
+++ b/public/crawlability-laguna-water-september-2026.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>הפניות זמניות (302/307): כתובת אחת (הבולטת: https://www.laguna-water.co.il/c/ברזים_למערכות_מים_תת_כיוריות, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>הפניות זמניות (302/307): כתובת אחת; הבולטת https://www.laguna-water.co.il/c/ברזים_למערכות_מים_תת_כיוריות (2 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308): 4 כתובות (הבולטת: https://www.laguna-water.co.il/page/שאלות_תשובות, 296 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים לכתובות שמפנות (301/308): 4 כתובות; הבולטת https://www.laguna-water.co.il/page/שאלות_תשובות (296 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לגרסת דומיין לא קנונית: 4 כתובות (הבולטת: https://laguna-water.co.il/p/טוחן_אשפה_Eco_Logic_10_אנהיים_ANAHEIM, 3 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים לגרסת דומיין לא קנונית: 4 כתובות; הבולטת https://laguna-water.co.il/p/טוחן_אשפה_Eco_Logic_10_אנהיים_ANAHEIM (3 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של laguna-water ב-SE Ranking (הסריקה האחרונה: 2026-02-02); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
+          <t>להריץ מחדש (בממשק) את ה-Website Audit של laguna-water ב-SE Ranking; הסריקה האחרונה: 2026-02-02.</t>
         </is>
       </c>
     </row>

--- a/public/crawlability-laguna-water-september-2026.xlsx
+++ b/public/crawlability-laguna-water-september-2026.xlsx
@@ -41,7 +41,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -68,11 +68,6 @@
         <fgColor rgb="00E2E3E5"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D1ECF1"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -86,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -101,9 +96,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -474,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -518,14 +510,14 @@
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>גבוהה</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>להסיר ממפת האתר כתובת אחת שמפנה ולהשאיר את כתובת היעד בלבד.</t>
+          <t>noindex על https://www.laguna-water.co.il/p/מסנן_למקרר_LG_מדגם_LT700 (17 קישורים נכנסים) ועל 9 עמודים נוספים: לאשר שזו הכוונה, אחרת להסיר את ההנחיה.</t>
         </is>
       </c>
     </row>
@@ -533,14 +525,14 @@
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>גבוהה</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>הפניות זמניות (302/307): כתובת אחת; הבולטת https://www.laguna-water.co.il/c/ברזים_למערכות_מים_תת_כיוריות (2 קישורים נכנסים).</t>
+          <t>קישורים פנימיים לכתובות שמפנות (301/308): 4 כתובות; הבולטת https://www.laguna-water.co.il/page/שאלות_תשובות (296 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -555,7 +547,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308): 4 כתובות; הבולטת https://www.laguna-water.co.il/page/שאלות_תשובות (296 קישורים נכנסים).</t>
+          <t>להסיר ממפת האתר כתובת אחת שמפנה.</t>
         </is>
       </c>
     </row>
@@ -563,14 +555,14 @@
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לגרסת דומיין לא קנונית: 4 כתובות; הבולטת https://laguna-water.co.il/p/טוחן_אשפה_Eco_Logic_10_אנהיים_ANAHEIM (3 קישורים נכנסים).</t>
+          <t>הפניות זמניות (302/307): כתובת אחת; הבולטת https://www.laguna-water.co.il/c/ברזים_למערכות_מים_תת_כיוריות (2 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -585,37 +577,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש (בממשק) את ה-Website Audit של laguna-water ב-SE Ranking; הסריקה האחרונה: 2026-02-02.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>לבדיקה</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>להחליט אם להסיר את חסימת סורקי ה-AI (Amazonbot) בקובץ robots.txt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>לבדיקה</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>לאשר ש-10 העמודים המוגדרים noindex אכן אמורים להישאר מחוץ לאינדקס.</t>
+          <t>קישורים פנימיים לגרסת דומיין לא קנונית: 4 כתובות; הבולטת https://laguna-water.co.il/p/טוחן_אשפה_Eco_Logic_10_אנהיים_ANAHEIM (3 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -704,7 +666,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/c/ברזים_למערכות_מים_תת_כיוריות</t>
         </is>
@@ -717,7 +679,7 @@
           <t>302 -&gt; 200</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/ברז_למערכת_תת_כיורית_חם_וקר_מתוצרת_Buder_טייוואן</t>
         </is>
@@ -728,7 +690,7 @@
       <c r="F2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/ברז_למערכת_תת_כיורית_חם_וקר_מתוצרת_Buder_טייוואן
 https://www.laguna-water.co.il/p/ברז_סטיקים_כרום__מוברש</t>
@@ -744,7 +706,7 @@
           <t>הפניה זמנית (302) לעמוד קיים. אם ההפניה מכוונת וקבועה, להמיר להפניית 301 ליעד ולעדכן את הקישורים הפנימיים ישירות ליעד; אם הכתובת המקורית אמורה לחזור, לבטל את ההפניה.</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/ברז_למערכת_תת_כיורית_חם_וקר_מתוצרת_Buder_טייוואן</t>
         </is>
@@ -840,7 +802,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/page/שאלות_תשובות</t>
         </is>
@@ -853,7 +815,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/</t>
         </is>
@@ -864,7 +826,7 @@
       <c r="F2" s="2" t="n">
         <v>296</v>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/
 https://www.laguna-water.co.il/p/ברז_אמבט_מקיר__מקט__BATHTAP01
@@ -889,19 +851,19 @@
           <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>גבוהה</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/c/מערכות_מים_קרים_ופושרים</t>
         </is>
@@ -914,7 +876,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/c/מתקן_מים_תת_כיורי</t>
         </is>
@@ -925,7 +887,7 @@
       <c r="F3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/מערכת_מים_קרים_תת_כיורית_Extra?refc=112056
 https://www.laguna-water.co.il/p/מערכת_מים_קרים_תת_כיורית_Extra</t>
@@ -941,7 +903,7 @@
           <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/c/מתקן_מים_תת_כיורי</t>
         </is>
@@ -953,7 +915,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/c/מערכות_מים_חמים_ופושרים</t>
         </is>
@@ -966,7 +928,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/c/מערכות_מים_חמים_וקרים</t>
         </is>
@@ -977,7 +939,7 @@
       <c r="F4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/page/טמפרטורה_מומלצת_להכנת_קפה_ותה</t>
         </is>
@@ -992,7 +954,7 @@
           <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/c/מערכות_מים_חמים_וקרים</t>
         </is>
@@ -1004,7 +966,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/c/מערכות_מים_חמים</t>
         </is>
@@ -1017,7 +979,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/c/מערכות_מים_חמים_וקרים</t>
         </is>
@@ -1028,7 +990,7 @@
       <c r="F5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/page/טמפרטורה_מומלצת_להכנת_קפה_ותה</t>
         </is>
@@ -1043,7 +1005,7 @@
           <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/c/מערכות_מים_חמים_וקרים</t>
         </is>
@@ -1055,7 +1017,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>https://laguna-water.co.il/p/טוחן_אשפה_Eco_Logic_10_אנהיים_ANAHEIM</t>
         </is>
@@ -1068,7 +1030,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/טוחן_אשפה_Eco_Logic_10_אנהיים_ANAHEIM</t>
         </is>
@@ -1079,7 +1041,7 @@
       <c r="F6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/מערכת_תת_כיורית_HOT_COLD_וסודה____כולל_טוחן_אשפה_אקולוג_יק_10_1_25_כס_והתקנה_חינם</t>
         </is>
@@ -1094,7 +1056,7 @@
           <t>קישור פנימי לגרסת דומיין לא קנונית (www/ללא www או http). לעדכן את הקישור לכתובת הקנונית.</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/טוחן_אשפה_Eco_Logic_10_אנהיים_ANAHEIM</t>
         </is>
@@ -1106,7 +1068,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>https://laguna-water.co.il/p/מתקן_מים_קרים_תת_כיורי_Buder_טיוואן</t>
         </is>
@@ -1119,7 +1081,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/מתקן_מים_קרים_תת_כיורי_Buder_טיוואן</t>
         </is>
@@ -1130,7 +1092,7 @@
       <c r="F7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/מתקן_מים_חמים_תת_כיורי_Buder_טיוואן
 https://www.laguna-water.co.il/p/ברז_למערכת_תת_כיורית_חם_וקר_מתוצרת_Buder_טייוואן</t>
@@ -1146,7 +1108,7 @@
           <t>קישור פנימי לגרסת דומיין לא קנונית (www/ללא www או http). לעדכן את הקישור לכתובת הקנונית.</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/מתקן_מים_קרים_תת_כיורי_Buder_טיוואן</t>
         </is>
@@ -1158,7 +1120,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>https://laguna-water.co.il/p/ברז_למערכת_תת_כיורית_חם_וקר_מתוצרת_Buder_טייוואן</t>
         </is>
@@ -1171,7 +1133,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/ברז_למערכת_תת_כיורית_חם_וקר_מתוצרת_Buder_טייוואן</t>
         </is>
@@ -1182,7 +1144,7 @@
       <c r="F8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/מתקן_מים_חמים_תת_כיורי_Buder_טיוואן</t>
         </is>
@@ -1197,7 +1159,7 @@
           <t>קישור פנימי לגרסת דומיין לא קנונית (www/ללא www או http). לעדכן את הקישור לכתובת הקנונית.</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/ברז_למערכת_תת_כיורית_חם_וקר_מתוצרת_Buder_טייוואן</t>
         </is>
@@ -1209,7 +1171,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>https://laguna-water.co.il/p/מתקן_מים_חמים_תת_כיורי_Buder_טיוואן</t>
         </is>
@@ -1222,7 +1184,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/מתקן_מים_חמים_תת_כיורי_Buder_טיוואן</t>
         </is>
@@ -1233,7 +1195,7 @@
       <c r="F9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/ברז_למערכת_תת_כיורית_חם_וקר_מתוצרת_Buder_טייוואן</t>
         </is>
@@ -1248,7 +1210,7 @@
           <t>קישור פנימי לגרסת דומיין לא קנונית (www/ללא www או http). לעדכן את הקישור לכתובת הקנונית.</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/מתקן_מים_חמים_תת_כיורי_Buder_טיוואן</t>
         </is>
@@ -1344,7 +1306,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/cdn-cgi/l/email-protection</t>
         </is>
@@ -1364,7 +1326,7 @@
       <c r="F2" s="2" t="n">
         <v>769</v>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/
 https://www.laguna-water.co.il/p/ברז_אמבט_מקיר__מקט__BATHTAP01
@@ -1467,7 +1429,7 @@
           <t>שורת Sitemap</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/crowlers/sitemap</t>
         </is>
@@ -1521,7 +1483,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/crowlers/sitemap</t>
         </is>
@@ -1565,12 +1527,12 @@
           <t>מפנה</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/page/שאלות_תשובות</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/</t>
         </is>
@@ -1582,7 +1544,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/</t>
         </is>
@@ -1592,7 +1554,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/ (0 הפניות)</t>
         </is>
@@ -1604,7 +1566,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>http://www.laguna-water.co.il/</t>
         </is>
@@ -1614,7 +1576,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>http://www.laguna-water.co.il/ (0 הפניות)</t>
         </is>
@@ -1626,7 +1588,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>https://laguna-water.co.il/</t>
         </is>
@@ -1636,7 +1598,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/ (1 הפניות)</t>
         </is>
@@ -1648,7 +1610,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>http://laguna-water.co.il/</t>
         </is>
@@ -1658,7 +1620,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/ (1 הפניות)</t>
         </is>
@@ -1729,7 +1691,7 @@
           <t>מסנן למקרר LG מדגם LT700 - מסננים | לגונה פתרונות מים</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/מסנן_למקרר_LG_מדגם_LT700</t>
         </is>
@@ -1751,7 +1713,7 @@
           <t>סננים למערכת MicroFilter M9 כולל ממברנה - מסננים</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/סט_החלפה_כולל_ממברנה_MicroFilter_M9</t>
         </is>
@@ -1773,7 +1735,7 @@
           <t>מסנן למקרר LG LT1000 - מסננים | לגונה פתרונות מים</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/פילטר_מקורי_למקרר_LG_LT1000</t>
         </is>
@@ -1795,7 +1757,7 @@
           <t>מערכת אוסמוזה הפוכה חשמלית KFLOW 400GPD מדגם X6 פרסטיג' !! SHOPPING IL  !!</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/מערכת_אוסמוזה_הפוכה_חשמלית_400GPD_מדגם_X6</t>
         </is>
@@ -1817,7 +1779,7 @@
           <t>טוחן אשפה InSinkErator Evolution 200 תוצרת ארה"ב 6 שנות אחריות</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/טוחן_אשפה_InSinkErator_דגם_EVOLUTION_200</t>
         </is>
@@ -1839,7 +1801,7 @@
           <t>טוחן אשפה InSinkErator Evolution 100 יבואן רשמי ניגא 5 שנות אחריות</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/InSinkErator_Evolution_100_יבואן_רשמי_ניגא_5_שנות_אחריות</t>
         </is>
@@ -1861,7 +1823,7 @@
           <t>טוחן אשפה InSinkErator ISE56 יבואן רשמי ניגא - 3 שנות אחריות</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/InSinkErator_ISE56_יבואן_רשמי_ניגא</t>
         </is>
@@ -1883,7 +1845,7 @@
           <t>טוחן אשפה InSinkErator ISE66 יבואן רשמי ניגא 4 שנות אחריות</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/InSinkErator_ISE66_יבואן_רשמי_ניגא</t>
         </is>
@@ -1905,7 +1867,7 @@
           <t>טוחן אשפה InSinkErator Evolution 250</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/טוחן_אשפה_InSinkErator_Evolution_250__תוצרת_ארהב</t>
         </is>
@@ -1927,7 +1889,7 @@
           <t>טוחן אשפה 1.25 כ"ס Eco Logic 10 אנהיים ANAHEIM</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>https://www.laguna-water.co.il/p/טוחן_אשפה_Eco_Logic_10_אנהיים_ANAHEIM</t>
         </is>

--- a/public/crawlability-laguna-water-september-2026.xlsx
+++ b/public/crawlability-laguna-water-september-2026.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -576,6 +576,21 @@
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>להוסיף תגית canonical לעמוד הבית (ולעמודי האתר).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>קישורים פנימיים לגרסת דומיין לא קנונית: 4 כתובות; הבולטת https://laguna-water.co.il/p/טוחן_אשפה_Eco_Logic_10_אנהיים_ANAHEIM (3 קישורים נכנסים).</t>
         </is>
